--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>136427850</v>
       </c>
       <c r="B4" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135784616</v>
+        <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>80580</v>
+        <v>92290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Putten, Hjd</t>
+          <t>Risåsen, Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408133</v>
+        <v>408568</v>
       </c>
       <c r="R2" t="n">
-        <v>6971019</v>
+        <v>6971042</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,74 +765,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784616</t>
+          <t>https://artportalen.se/Sighting/136811216</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127939548</v>
+        <v>136810515</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>80592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra risåsvägen, Beten, Storsjö, Hjd</t>
+          <t>Risåsen, Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408153</v>
+        <v>408534</v>
       </c>
       <c r="R3" t="n">
-        <v>6970967</v>
+        <v>6971136</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,74 +867,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127939548</t>
+          <t>https://artportalen.se/Sighting/136810515</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136427850</v>
+        <v>136810955</v>
       </c>
       <c r="B4" t="n">
-        <v>58164</v>
+        <v>80592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103023</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västra risåsvägen, Beten, Storsjö, Hjd</t>
+          <t>Risåsen, Risåsen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408117</v>
+        <v>408554</v>
       </c>
       <c r="R4" t="n">
-        <v>6971138</v>
+        <v>6971017</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,18 +969,1376 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136810955</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136811382</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80592</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Risåsen, Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>408498</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971041</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136811382</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136811755</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80592</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Risåsen, Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>408161</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6970937</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136811755</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136810361</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92074</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Risåsen, Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>408467</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6971247</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136810361</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136811403</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Risåsen, Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>408513</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6971076</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136811403</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136810504</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80595</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Risåsen, Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>408528</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6971171</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136810504</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135784616</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80580</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>408133</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971019</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784616</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136810443</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80596</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Risåsen, Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>408476</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971240</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136810443</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136811545</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80596</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Risåsen, Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>408433</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6971046</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136811545</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136811011</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80602</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Risåsen, Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>408555</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6971016</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136811011</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136811768</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80602</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Risåsen, Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>408159</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6970932</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136811768</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127939548</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Västra risåsvägen, Beten, Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>408153</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6970967</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127939548</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136427850</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Västra risåsvägen, Beten, Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>408117</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6971138</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136427850</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136811029</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Risåsen, Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>408555</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6971016</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136811029</t>
         </is>
       </c>
     </row>
@@ -1017,6 +2347,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810515</v>
       </c>
       <c r="B3" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136810955</v>
       </c>
       <c r="B4" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136811382</v>
       </c>
       <c r="B5" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136811755</v>
       </c>
       <c r="B6" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136811403</v>
       </c>
       <c r="B8" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136810504</v>
       </c>
       <c r="B9" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136810443</v>
       </c>
       <c r="B11" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136811545</v>
       </c>
       <c r="B12" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136811011</v>
       </c>
       <c r="B13" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136811768</v>
       </c>
       <c r="B14" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810515</v>
       </c>
       <c r="B3" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136810955</v>
       </c>
       <c r="B4" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136811382</v>
       </c>
       <c r="B5" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136811755</v>
       </c>
       <c r="B6" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136811403</v>
       </c>
       <c r="B8" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136810504</v>
       </c>
       <c r="B9" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136810443</v>
       </c>
       <c r="B11" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136811545</v>
       </c>
       <c r="B12" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136811011</v>
       </c>
       <c r="B13" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136811768</v>
       </c>
       <c r="B14" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810515</v>
       </c>
       <c r="B3" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136810955</v>
       </c>
       <c r="B4" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136811382</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136811755</v>
       </c>
       <c r="B6" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136811403</v>
       </c>
       <c r="B8" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136810504</v>
       </c>
       <c r="B9" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136810443</v>
       </c>
       <c r="B11" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136811545</v>
       </c>
       <c r="B12" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136811011</v>
       </c>
       <c r="B13" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136811768</v>
       </c>
       <c r="B14" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810515</v>
       </c>
       <c r="B3" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136810955</v>
       </c>
       <c r="B4" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136811382</v>
       </c>
       <c r="B5" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136811755</v>
       </c>
       <c r="B6" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136811403</v>
       </c>
       <c r="B8" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136810504</v>
       </c>
       <c r="B9" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136810443</v>
       </c>
       <c r="B11" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136811545</v>
       </c>
       <c r="B12" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136811011</v>
       </c>
       <c r="B13" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136811768</v>
       </c>
       <c r="B14" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810515</v>
       </c>
       <c r="B3" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136810955</v>
       </c>
       <c r="B4" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136811382</v>
       </c>
       <c r="B5" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136811755</v>
       </c>
       <c r="B6" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136811403</v>
       </c>
       <c r="B8" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136810504</v>
       </c>
       <c r="B9" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136810443</v>
       </c>
       <c r="B11" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136811545</v>
       </c>
       <c r="B12" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136811011</v>
       </c>
       <c r="B13" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136811768</v>
       </c>
       <c r="B14" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810515</v>
       </c>
       <c r="B3" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136810955</v>
       </c>
       <c r="B4" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136811382</v>
       </c>
       <c r="B5" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136811755</v>
       </c>
       <c r="B6" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136811403</v>
       </c>
       <c r="B8" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136810504</v>
       </c>
       <c r="B9" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136810443</v>
       </c>
       <c r="B11" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136811545</v>
       </c>
       <c r="B12" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136811011</v>
       </c>
       <c r="B13" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136811768</v>
       </c>
       <c r="B14" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136811029</v>
       </c>
       <c r="B17" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810515</v>
       </c>
       <c r="B3" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136810955</v>
       </c>
       <c r="B4" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136811382</v>
       </c>
       <c r="B5" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136811755</v>
       </c>
       <c r="B6" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136811403</v>
       </c>
       <c r="B8" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136810504</v>
       </c>
       <c r="B9" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136810443</v>
       </c>
       <c r="B11" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136811545</v>
       </c>
       <c r="B12" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136811011</v>
       </c>
       <c r="B13" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136811768</v>
       </c>
       <c r="B14" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136811029</v>
       </c>
       <c r="B17" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810515</v>
       </c>
       <c r="B3" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136810955</v>
       </c>
       <c r="B4" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136811382</v>
       </c>
       <c r="B5" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136811755</v>
       </c>
       <c r="B6" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136811403</v>
       </c>
       <c r="B8" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136810504</v>
       </c>
       <c r="B9" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136810443</v>
       </c>
       <c r="B11" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136811545</v>
       </c>
       <c r="B12" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136811011</v>
       </c>
       <c r="B13" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136811768</v>
       </c>
       <c r="B14" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136811029</v>
       </c>
       <c r="B17" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810515</v>
       </c>
       <c r="B3" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136810955</v>
       </c>
       <c r="B4" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136811382</v>
       </c>
       <c r="B5" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136811755</v>
       </c>
       <c r="B6" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136811403</v>
       </c>
       <c r="B8" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136810504</v>
       </c>
       <c r="B9" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136810443</v>
       </c>
       <c r="B11" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136811545</v>
       </c>
       <c r="B12" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136811011</v>
       </c>
       <c r="B13" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136811768</v>
       </c>
       <c r="B14" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136811029</v>
       </c>
       <c r="B17" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60833-2025 artfynd.xlsx
+++ b/artfynd/A 60833-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136811216</v>
       </c>
       <c r="B2" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810515</v>
       </c>
       <c r="B3" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136810955</v>
       </c>
       <c r="B4" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136811382</v>
       </c>
       <c r="B5" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136811755</v>
       </c>
       <c r="B6" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136810361</v>
       </c>
       <c r="B7" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136811403</v>
       </c>
       <c r="B8" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136810504</v>
       </c>
       <c r="B9" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136810443</v>
       </c>
       <c r="B11" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136811545</v>
       </c>
       <c r="B12" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136811011</v>
       </c>
       <c r="B13" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136811768</v>
       </c>
       <c r="B14" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136811029</v>
       </c>
       <c r="B17" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
